--- a/VerveStacks_ARE_grids_kan/source_data/VerveStacks_ARE.xlsx
+++ b/VerveStacks_ARE_grids_kan/source_data/VerveStacks_ARE.xlsx
@@ -1,23 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\VerveStacks\output\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{3D6A0AE5-4890-4B92-AF31-FDF8555DB4C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{ED778446-A099-469D-B7ED-6FAC5DDB21A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="weo_pg" sheetId="13" r:id="rId1"/>
-    <sheet name="re_targets" sheetId="12" r:id="rId2"/>
-    <sheet name="ccs_retrofits" sheetId="11" r:id="rId3"/>
-    <sheet name="Calibration" sheetId="10" r:id="rId4"/>
-    <sheet name="existing_stock" sheetId="9" r:id="rId5"/>
+    <sheet name="weo_pg" sheetId="18" r:id="rId1"/>
+    <sheet name="re_targets" sheetId="17" r:id="rId2"/>
+    <sheet name="ccs_retrofits" sheetId="16" r:id="rId3"/>
+    <sheet name="Calibration" sheetId="15" r:id="rId4"/>
+    <sheet name="existing_stock" sheetId="14" r:id="rId5"/>
     <sheet name="historical_data_long" sheetId="5" r:id="rId6"/>
     <sheet name="historical_data" sheetId="4" r:id="rId7"/>
     <sheet name="system_settings" sheetId="1" r:id="rId8"/>
@@ -2249,7 +2249,7 @@
         <xdr:cNvPr id="3" name="Picture 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FC7743F1-4AF3-18D3-6071-0EB8D51EB4EA}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7D406DD3-49AA-C633-491B-69D891472517}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2304,7 +2304,7 @@
         <xdr:cNvPr id="3" name="Picture 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{07DD0ACF-82CE-A02A-D77E-07A5D634CD06}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{560CFE31-E716-00D2-AE75-90190705A266}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2655,7 +2655,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EECA8EB2-7D21-47FE-A039-4AB1B88F40C7}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BBD81107-6CBF-41F8-B011-978997C6D868}">
   <dimension ref="B2:I111"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -5342,7 +5342,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6EDCD6B9-0BD6-4E4D-9AF2-FACC63161190}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D814E320-07AB-4279-AE0F-FE3879ADDB24}">
   <dimension ref="B2:L5"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -5462,7 +5462,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F32A6EC0-FEBF-4AA2-907F-E98F939DD5AD}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DA638C34-7431-4789-8606-B4CD5E5F787E}">
   <dimension ref="B2:J132"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -5508,22 +5508,22 @@
         <v>432</v>
       </c>
       <c r="D4">
-        <v>1967</v>
+        <v>2445</v>
       </c>
       <c r="E4">
-        <v>25.2</v>
+        <v>30.4</v>
       </c>
       <c r="F4">
-        <v>2.73</v>
+        <v>3.52</v>
       </c>
       <c r="G4">
-        <v>0.30867165000000002</v>
+        <v>0.19653039000000003</v>
       </c>
       <c r="H4">
-        <v>0.76759999999999995</v>
+        <v>0.72770000000000001</v>
       </c>
       <c r="I4">
-        <v>0.40455000000000002</v>
+        <v>0.28318500000000002</v>
       </c>
       <c r="J4" t="s">
         <v>96</v>
@@ -5537,22 +5537,22 @@
         <v>433</v>
       </c>
       <c r="D5">
-        <v>1967</v>
+        <v>2445</v>
       </c>
       <c r="E5">
-        <v>25.2</v>
+        <v>30.4</v>
       </c>
       <c r="F5">
-        <v>2.73</v>
+        <v>3.52</v>
       </c>
       <c r="G5">
-        <v>0.31576755000000001</v>
+        <v>0.20104833000000003</v>
       </c>
       <c r="H5">
-        <v>0.76759999999999995</v>
+        <v>0.72770000000000001</v>
       </c>
       <c r="I5">
-        <v>0.41385000000000005</v>
+        <v>0.28969500000000004</v>
       </c>
       <c r="J5" t="s">
         <v>100</v>
@@ -5575,13 +5575,13 @@
         <v>3.75</v>
       </c>
       <c r="G6">
-        <v>0.28982625000000001</v>
+        <v>0.22461534375000003</v>
       </c>
       <c r="H6">
         <v>0.84455000000000002</v>
       </c>
       <c r="I6">
-        <v>0.33123000000000002</v>
+        <v>0.25670325000000005</v>
       </c>
       <c r="J6" t="s">
         <v>614</v>
@@ -5604,13 +5604,13 @@
         <v>3.75</v>
       </c>
       <c r="G7">
-        <v>0.28982625000000001</v>
+        <v>0.22461534375000003</v>
       </c>
       <c r="H7">
         <v>0.84455000000000002</v>
       </c>
       <c r="I7">
-        <v>0.33123000000000002</v>
+        <v>0.25670325000000005</v>
       </c>
       <c r="J7" t="s">
         <v>616</v>
@@ -5633,13 +5633,13 @@
         <v>3.75</v>
       </c>
       <c r="G8">
-        <v>0.28982625000000001</v>
+        <v>0.22461534375000003</v>
       </c>
       <c r="H8">
         <v>0.84455000000000002</v>
       </c>
       <c r="I8">
-        <v>0.33123000000000002</v>
+        <v>0.25670325000000005</v>
       </c>
       <c r="J8" t="s">
         <v>618</v>
@@ -5662,13 +5662,13 @@
         <v>3.75</v>
       </c>
       <c r="G9">
-        <v>0.28982625000000001</v>
+        <v>0.22461534375000003</v>
       </c>
       <c r="H9">
         <v>0.84455000000000002</v>
       </c>
       <c r="I9">
-        <v>0.33123000000000002</v>
+        <v>0.25670325000000005</v>
       </c>
       <c r="J9" t="s">
         <v>620</v>
@@ -5691,13 +5691,13 @@
         <v>3.75</v>
       </c>
       <c r="G10">
-        <v>0.44349375000000002</v>
+        <v>0.34370765625000005</v>
       </c>
       <c r="H10">
         <v>0.84455000000000002</v>
       </c>
       <c r="I10">
-        <v>0.50685000000000002</v>
+        <v>0.39280875000000004</v>
       </c>
       <c r="J10" t="s">
         <v>102</v>
@@ -5720,13 +5720,13 @@
         <v>3.75</v>
       </c>
       <c r="G11">
-        <v>0.47197499999999998</v>
+        <v>0.36578062500000003</v>
       </c>
       <c r="H11">
         <v>0.84455000000000002</v>
       </c>
       <c r="I11">
-        <v>0.53939999999999999</v>
+        <v>0.41803500000000005</v>
       </c>
       <c r="J11" t="s">
         <v>106</v>
@@ -5749,13 +5749,13 @@
         <v>3.75</v>
       </c>
       <c r="G12">
-        <v>0.47197499999999998</v>
+        <v>0.36578062500000003</v>
       </c>
       <c r="H12">
         <v>0.84455000000000002</v>
       </c>
       <c r="I12">
-        <v>0.53939999999999999</v>
+        <v>0.41803499999999999</v>
       </c>
       <c r="J12" t="s">
         <v>109</v>
@@ -5778,13 +5778,13 @@
         <v>3.75</v>
       </c>
       <c r="G13">
-        <v>0.47197499999999998</v>
+        <v>0.36578062500000003</v>
       </c>
       <c r="H13">
         <v>0.84455000000000002</v>
       </c>
       <c r="I13">
-        <v>0.53939999999999999</v>
+        <v>0.41803500000000005</v>
       </c>
       <c r="J13" t="s">
         <v>111</v>
@@ -5807,13 +5807,13 @@
         <v>3.75</v>
       </c>
       <c r="G14">
-        <v>0.48825000000000002</v>
+        <v>0.37839375000000003</v>
       </c>
       <c r="H14">
         <v>0.84455000000000002</v>
       </c>
       <c r="I14">
-        <v>0.55800000000000005</v>
+        <v>0.43245000000000006</v>
       </c>
       <c r="J14" t="s">
         <v>113</v>
@@ -5836,13 +5836,13 @@
         <v>3.75</v>
       </c>
       <c r="G15">
-        <v>0.42721875000000004</v>
+        <v>0.3310945312500001</v>
       </c>
       <c r="H15">
         <v>0.84455000000000002</v>
       </c>
       <c r="I15">
-        <v>0.48825000000000007</v>
+        <v>0.37839375000000008</v>
       </c>
       <c r="J15" t="s">
         <v>116</v>
@@ -5865,13 +5865,13 @@
         <v>3.75</v>
       </c>
       <c r="G16">
-        <v>0.36618750000000005</v>
+        <v>0.28379531250000006</v>
       </c>
       <c r="H16">
         <v>0.84455000000000002</v>
       </c>
       <c r="I16">
-        <v>0.41850000000000009</v>
+        <v>0.32433750000000006</v>
       </c>
       <c r="J16" t="s">
         <v>118</v>
@@ -5894,13 +5894,13 @@
         <v>3.75</v>
       </c>
       <c r="G17">
-        <v>0.44349375000000002</v>
+        <v>0.34370765625000005</v>
       </c>
       <c r="H17">
         <v>0.84455000000000002</v>
       </c>
       <c r="I17">
-        <v>0.50685000000000002</v>
+        <v>0.39280875000000004</v>
       </c>
       <c r="J17" t="s">
         <v>120</v>
@@ -5923,13 +5923,13 @@
         <v>3.75</v>
       </c>
       <c r="G18">
-        <v>0.44349375000000002</v>
+        <v>0.34370765625000005</v>
       </c>
       <c r="H18">
         <v>0.84455000000000002</v>
       </c>
       <c r="I18">
-        <v>0.50685000000000002</v>
+        <v>0.39280875000000004</v>
       </c>
       <c r="J18" t="s">
         <v>122</v>
@@ -5952,13 +5952,13 @@
         <v>3.75</v>
       </c>
       <c r="G19">
-        <v>0.44349375000000002</v>
+        <v>0.34370765625000005</v>
       </c>
       <c r="H19">
         <v>0.84455000000000002</v>
       </c>
       <c r="I19">
-        <v>0.50685000000000002</v>
+        <v>0.39280875000000004</v>
       </c>
       <c r="J19" t="s">
         <v>124</v>
@@ -5981,13 +5981,13 @@
         <v>3.75</v>
       </c>
       <c r="G20">
-        <v>0.47197499999999998</v>
+        <v>0.36578062500000003</v>
       </c>
       <c r="H20">
         <v>0.84455000000000002</v>
       </c>
       <c r="I20">
-        <v>0.53939999999999999</v>
+        <v>0.41803499999999999</v>
       </c>
       <c r="J20" t="s">
         <v>126</v>
@@ -6010,13 +6010,13 @@
         <v>3.75</v>
       </c>
       <c r="G21">
-        <v>0.47197499999999998</v>
+        <v>0.36578062500000003</v>
       </c>
       <c r="H21">
         <v>0.84455000000000002</v>
       </c>
       <c r="I21">
-        <v>0.53939999999999999</v>
+        <v>0.41803499999999999</v>
       </c>
       <c r="J21" t="s">
         <v>128</v>
@@ -6039,13 +6039,13 @@
         <v>3.75</v>
       </c>
       <c r="G22">
-        <v>0.47197499999999998</v>
+        <v>0.36578062500000003</v>
       </c>
       <c r="H22">
         <v>0.84455000000000002</v>
       </c>
       <c r="I22">
-        <v>0.53939999999999999</v>
+        <v>0.41803499999999999</v>
       </c>
       <c r="J22" t="s">
         <v>130</v>
@@ -6068,13 +6068,13 @@
         <v>3.75</v>
       </c>
       <c r="G23">
-        <v>0.47197499999999998</v>
+        <v>0.36578062500000003</v>
       </c>
       <c r="H23">
         <v>0.84455000000000002</v>
       </c>
       <c r="I23">
-        <v>0.53939999999999999</v>
+        <v>0.41803499999999999</v>
       </c>
       <c r="J23" t="s">
         <v>132</v>
@@ -6097,13 +6097,13 @@
         <v>3.75</v>
       </c>
       <c r="G24">
-        <v>0.48825000000000002</v>
+        <v>0.37839375000000003</v>
       </c>
       <c r="H24">
         <v>0.84455000000000002</v>
       </c>
       <c r="I24">
-        <v>0.55800000000000005</v>
+        <v>0.43245000000000006</v>
       </c>
       <c r="J24" t="s">
         <v>134</v>
@@ -6126,13 +6126,13 @@
         <v>3.75</v>
       </c>
       <c r="G25">
-        <v>0.47197499999999998</v>
+        <v>0.36578062500000003</v>
       </c>
       <c r="H25">
         <v>0.84455000000000002</v>
       </c>
       <c r="I25">
-        <v>0.53939999999999999</v>
+        <v>0.41803499999999999</v>
       </c>
       <c r="J25" t="s">
         <v>137</v>
@@ -6155,13 +6155,13 @@
         <v>3.75</v>
       </c>
       <c r="G26">
-        <v>0.48825000000000002</v>
+        <v>0.37839375000000003</v>
       </c>
       <c r="H26">
         <v>0.84455000000000002</v>
       </c>
       <c r="I26">
-        <v>0.55800000000000005</v>
+        <v>0.43245000000000006</v>
       </c>
       <c r="J26" t="s">
         <v>140</v>
@@ -6184,13 +6184,13 @@
         <v>3.75</v>
       </c>
       <c r="G27">
-        <v>0.48825000000000002</v>
+        <v>0.37839375000000003</v>
       </c>
       <c r="H27">
         <v>0.84455000000000002</v>
       </c>
       <c r="I27">
-        <v>0.55800000000000005</v>
+        <v>0.43245000000000006</v>
       </c>
       <c r="J27" t="s">
         <v>142</v>
@@ -6213,13 +6213,13 @@
         <v>3.75</v>
       </c>
       <c r="G28">
-        <v>0.48825000000000002</v>
+        <v>0.37839375000000003</v>
       </c>
       <c r="H28">
         <v>0.84455000000000002</v>
       </c>
       <c r="I28">
-        <v>0.55800000000000005</v>
+        <v>0.43245000000000006</v>
       </c>
       <c r="J28" t="s">
         <v>144</v>
@@ -6242,13 +6242,13 @@
         <v>3.75</v>
       </c>
       <c r="G29">
-        <v>0.44349375000000002</v>
+        <v>0.34370765625000005</v>
       </c>
       <c r="H29">
         <v>0.84455000000000002</v>
       </c>
       <c r="I29">
-        <v>0.50685000000000002</v>
+        <v>0.39280875000000004</v>
       </c>
       <c r="J29" t="s">
         <v>146</v>
@@ -6271,13 +6271,13 @@
         <v>3.75</v>
       </c>
       <c r="G30">
-        <v>0.47197499999999998</v>
+        <v>0.36578062499999997</v>
       </c>
       <c r="H30">
         <v>0.84455000000000002</v>
       </c>
       <c r="I30">
-        <v>0.53939999999999999</v>
+        <v>0.41803499999999993</v>
       </c>
       <c r="J30" t="s">
         <v>149</v>
@@ -6300,13 +6300,13 @@
         <v>3.75</v>
       </c>
       <c r="G31">
-        <v>0.47197499999999998</v>
+        <v>0.36578062499999997</v>
       </c>
       <c r="H31">
         <v>0.84455000000000002</v>
       </c>
       <c r="I31">
-        <v>0.53939999999999999</v>
+        <v>0.41803499999999993</v>
       </c>
       <c r="J31" t="s">
         <v>151</v>
@@ -6329,13 +6329,13 @@
         <v>3.75</v>
       </c>
       <c r="G32">
-        <v>0.47197499999999998</v>
+        <v>0.36578062500000003</v>
       </c>
       <c r="H32">
         <v>0.84455000000000002</v>
       </c>
       <c r="I32">
-        <v>0.53939999999999999</v>
+        <v>0.41803499999999999</v>
       </c>
       <c r="J32" t="s">
         <v>153</v>
@@ -6358,13 +6358,13 @@
         <v>3.75</v>
       </c>
       <c r="G33">
-        <v>0.47197499999999998</v>
+        <v>0.36578062500000003</v>
       </c>
       <c r="H33">
         <v>0.84455000000000002</v>
       </c>
       <c r="I33">
-        <v>0.53939999999999999</v>
+        <v>0.41803499999999999</v>
       </c>
       <c r="J33" t="s">
         <v>155</v>
@@ -6387,13 +6387,13 @@
         <v>3.75</v>
       </c>
       <c r="G34">
-        <v>0.44349375000000002</v>
+        <v>0.34370765625000005</v>
       </c>
       <c r="H34">
         <v>0.84455000000000002</v>
       </c>
       <c r="I34">
-        <v>0.50685000000000002</v>
+        <v>0.39280875000000004</v>
       </c>
       <c r="J34" t="s">
         <v>157</v>
@@ -6416,13 +6416,13 @@
         <v>3.75</v>
       </c>
       <c r="G35">
-        <v>0.44349375000000002</v>
+        <v>0.34370765625000005</v>
       </c>
       <c r="H35">
         <v>0.84455000000000002</v>
       </c>
       <c r="I35">
-        <v>0.50685000000000002</v>
+        <v>0.39280875000000004</v>
       </c>
       <c r="J35" t="s">
         <v>160</v>
@@ -6445,13 +6445,13 @@
         <v>3.75</v>
       </c>
       <c r="G36">
-        <v>0.44349375000000002</v>
+        <v>0.34370765625000005</v>
       </c>
       <c r="H36">
         <v>0.84455000000000002</v>
       </c>
       <c r="I36">
-        <v>0.50685000000000002</v>
+        <v>0.39280875000000004</v>
       </c>
       <c r="J36" t="s">
         <v>162</v>
@@ -6474,13 +6474,13 @@
         <v>3.75</v>
       </c>
       <c r="G37">
-        <v>0.44349375000000002</v>
+        <v>0.34370765625000005</v>
       </c>
       <c r="H37">
         <v>0.84455000000000002</v>
       </c>
       <c r="I37">
-        <v>0.50685000000000002</v>
+        <v>0.39280875000000004</v>
       </c>
       <c r="J37" t="s">
         <v>164</v>
@@ -6503,13 +6503,13 @@
         <v>3.75</v>
       </c>
       <c r="G38">
-        <v>0.48825000000000002</v>
+        <v>0.37839375000000003</v>
       </c>
       <c r="H38">
         <v>0.84455000000000002</v>
       </c>
       <c r="I38">
-        <v>0.55800000000000005</v>
+        <v>0.43245000000000006</v>
       </c>
       <c r="J38" t="s">
         <v>166</v>
@@ -6532,13 +6532,13 @@
         <v>3.75</v>
       </c>
       <c r="G39">
-        <v>0.32550000000000007</v>
+        <v>0.25226250000000006</v>
       </c>
       <c r="H39">
         <v>0.84455000000000002</v>
       </c>
       <c r="I39">
-        <v>0.37200000000000005</v>
+        <v>0.28830000000000006</v>
       </c>
       <c r="J39" t="s">
         <v>168</v>
@@ -6561,13 +6561,13 @@
         <v>3.75</v>
       </c>
       <c r="G40">
-        <v>0.47197499999999998</v>
+        <v>0.36578062500000003</v>
       </c>
       <c r="H40">
         <v>0.84455000000000002</v>
       </c>
       <c r="I40">
-        <v>0.53939999999999999</v>
+        <v>0.41803499999999999</v>
       </c>
       <c r="J40" t="s">
         <v>170</v>
@@ -6590,13 +6590,13 @@
         <v>3.75</v>
       </c>
       <c r="G41">
-        <v>0.44349375000000002</v>
+        <v>0.34370765625000005</v>
       </c>
       <c r="H41">
         <v>0.84455000000000002</v>
       </c>
       <c r="I41">
-        <v>0.50685000000000002</v>
+        <v>0.39280875000000004</v>
       </c>
       <c r="J41" t="s">
         <v>172</v>
@@ -6619,13 +6619,13 @@
         <v>3.75</v>
       </c>
       <c r="G42">
-        <v>0.44349375000000002</v>
+        <v>0.34370765625000005</v>
       </c>
       <c r="H42">
         <v>0.84455000000000002</v>
       </c>
       <c r="I42">
-        <v>0.50685000000000002</v>
+        <v>0.39280875000000004</v>
       </c>
       <c r="J42" t="s">
         <v>174</v>
@@ -6648,13 +6648,13 @@
         <v>3.75</v>
       </c>
       <c r="G43">
-        <v>0.48825000000000002</v>
+        <v>0.37839375000000003</v>
       </c>
       <c r="H43">
         <v>0.84455000000000002</v>
       </c>
       <c r="I43">
-        <v>0.55800000000000005</v>
+        <v>0.43245000000000006</v>
       </c>
       <c r="J43" t="s">
         <v>176</v>
@@ -6677,13 +6677,13 @@
         <v>3.75</v>
       </c>
       <c r="G44">
-        <v>0.44349375000000002</v>
+        <v>0.3437076562500001</v>
       </c>
       <c r="H44">
         <v>0.84455000000000002</v>
       </c>
       <c r="I44">
-        <v>0.50685000000000002</v>
+        <v>0.3928087500000001</v>
       </c>
       <c r="J44" t="s">
         <v>178</v>
@@ -6706,13 +6706,13 @@
         <v>3.75</v>
       </c>
       <c r="G45">
-        <v>0.18716250000000001</v>
+        <v>0.14505093750000003</v>
       </c>
       <c r="H45">
         <v>0.84455000000000002</v>
       </c>
       <c r="I45">
-        <v>0.21390000000000001</v>
+        <v>0.16577250000000002</v>
       </c>
       <c r="J45" t="s">
         <v>180</v>
@@ -6735,13 +6735,13 @@
         <v>3.75</v>
       </c>
       <c r="G46">
-        <v>0.18716250000000001</v>
+        <v>0.14505093750000003</v>
       </c>
       <c r="H46">
         <v>0.84455000000000002</v>
       </c>
       <c r="I46">
-        <v>0.21390000000000001</v>
+        <v>0.16577250000000002</v>
       </c>
       <c r="J46" t="s">
         <v>183</v>
@@ -6764,13 +6764,13 @@
         <v>3.75</v>
       </c>
       <c r="G47">
-        <v>0.21564375000000005</v>
+        <v>0.16712390625000001</v>
       </c>
       <c r="H47">
         <v>0.84455000000000002</v>
       </c>
       <c r="I47">
-        <v>0.24645000000000006</v>
+        <v>0.19099875000000002</v>
       </c>
       <c r="J47" t="s">
         <v>185</v>
@@ -6793,13 +6793,13 @@
         <v>3.75</v>
       </c>
       <c r="G48">
-        <v>0.21564375000000005</v>
+        <v>0.16712390625000001</v>
       </c>
       <c r="H48">
         <v>0.84455000000000002</v>
       </c>
       <c r="I48">
-        <v>0.24645000000000006</v>
+        <v>0.19099875000000002</v>
       </c>
       <c r="J48" t="s">
         <v>187</v>
@@ -6822,13 +6822,13 @@
         <v>3.75</v>
       </c>
       <c r="G49">
-        <v>0.21564375000000005</v>
+        <v>0.16712390625000001</v>
       </c>
       <c r="H49">
         <v>0.84455000000000002</v>
       </c>
       <c r="I49">
-        <v>0.24645000000000006</v>
+        <v>0.19099875000000002</v>
       </c>
       <c r="J49" t="s">
         <v>189</v>
@@ -6851,13 +6851,13 @@
         <v>3.75</v>
       </c>
       <c r="G50">
-        <v>0.21564375000000005</v>
+        <v>0.16712390625000001</v>
       </c>
       <c r="H50">
         <v>0.84455000000000002</v>
       </c>
       <c r="I50">
-        <v>0.24645000000000006</v>
+        <v>0.19099875000000002</v>
       </c>
       <c r="J50" t="s">
         <v>191</v>
@@ -6880,13 +6880,13 @@
         <v>3.75</v>
       </c>
       <c r="G51">
-        <v>0.21564375000000005</v>
+        <v>0.16712390625000001</v>
       </c>
       <c r="H51">
         <v>0.84455000000000002</v>
       </c>
       <c r="I51">
-        <v>0.24645000000000006</v>
+        <v>0.19099875000000002</v>
       </c>
       <c r="J51" t="s">
         <v>193</v>
@@ -6909,13 +6909,13 @@
         <v>3.75</v>
       </c>
       <c r="G52">
-        <v>0.21564375000000005</v>
+        <v>0.16712390625000001</v>
       </c>
       <c r="H52">
         <v>0.84455000000000002</v>
       </c>
       <c r="I52">
-        <v>0.24645000000000006</v>
+        <v>0.19099875000000002</v>
       </c>
       <c r="J52" t="s">
         <v>195</v>
@@ -6938,13 +6938,13 @@
         <v>3.75</v>
       </c>
       <c r="G53">
-        <v>0.23598749999999999</v>
+        <v>0.18289031250000001</v>
       </c>
       <c r="H53">
         <v>0.84455000000000002</v>
       </c>
       <c r="I53">
-        <v>0.2697</v>
+        <v>0.20901749999999999</v>
       </c>
       <c r="J53" t="s">
         <v>197</v>
@@ -6967,13 +6967,13 @@
         <v>3.75</v>
       </c>
       <c r="G54">
-        <v>0.23598749999999999</v>
+        <v>0.18289031250000001</v>
       </c>
       <c r="H54">
         <v>0.84455000000000002</v>
       </c>
       <c r="I54">
-        <v>0.2697</v>
+        <v>0.20901749999999999</v>
       </c>
       <c r="J54" t="s">
         <v>199</v>
@@ -6996,13 +6996,13 @@
         <v>3.75</v>
       </c>
       <c r="G55">
-        <v>0.23598749999999999</v>
+        <v>0.18289031250000001</v>
       </c>
       <c r="H55">
         <v>0.84455000000000002</v>
       </c>
       <c r="I55">
-        <v>0.2697</v>
+        <v>0.20901749999999999</v>
       </c>
       <c r="J55" t="s">
         <v>201</v>
@@ -7025,13 +7025,13 @@
         <v>3.75</v>
       </c>
       <c r="G56">
-        <v>0.23598749999999999</v>
+        <v>0.18289031250000001</v>
       </c>
       <c r="H56">
         <v>0.84455000000000002</v>
       </c>
       <c r="I56">
-        <v>0.2697</v>
+        <v>0.20901749999999999</v>
       </c>
       <c r="J56" t="s">
         <v>203</v>
@@ -7054,13 +7054,13 @@
         <v>3.75</v>
       </c>
       <c r="G57">
-        <v>0.23598749999999999</v>
+        <v>0.18289031250000001</v>
       </c>
       <c r="H57">
         <v>0.84455000000000002</v>
       </c>
       <c r="I57">
-        <v>0.2697</v>
+        <v>0.20901749999999999</v>
       </c>
       <c r="J57" t="s">
         <v>205</v>
@@ -7083,13 +7083,13 @@
         <v>3.75</v>
       </c>
       <c r="G58">
-        <v>0.23598749999999999</v>
+        <v>0.18289031250000001</v>
       </c>
       <c r="H58">
         <v>0.84455000000000002</v>
       </c>
       <c r="I58">
-        <v>0.2697</v>
+        <v>0.20901749999999999</v>
       </c>
       <c r="J58" t="s">
         <v>207</v>
@@ -7112,13 +7112,13 @@
         <v>3.75</v>
       </c>
       <c r="G59">
-        <v>0.23598749999999999</v>
+        <v>0.18289031250000001</v>
       </c>
       <c r="H59">
         <v>0.84455000000000002</v>
       </c>
       <c r="I59">
-        <v>0.2697</v>
+        <v>0.20901749999999999</v>
       </c>
       <c r="J59" t="s">
         <v>209</v>
@@ -7141,13 +7141,13 @@
         <v>3.75</v>
       </c>
       <c r="G60">
-        <v>0.26040000000000002</v>
+        <v>0.20181000000000004</v>
       </c>
       <c r="H60">
         <v>0.84455000000000002</v>
       </c>
       <c r="I60">
-        <v>0.29760000000000003</v>
+        <v>0.23064000000000004</v>
       </c>
       <c r="J60" t="s">
         <v>211</v>
@@ -7170,13 +7170,13 @@
         <v>3.75</v>
       </c>
       <c r="G61">
-        <v>0.26040000000000002</v>
+        <v>0.20181000000000004</v>
       </c>
       <c r="H61">
         <v>0.84455000000000002</v>
       </c>
       <c r="I61">
-        <v>0.29760000000000003</v>
+        <v>0.23064000000000004</v>
       </c>
       <c r="J61" t="s">
         <v>213</v>
@@ -7199,13 +7199,13 @@
         <v>3.75</v>
       </c>
       <c r="G62">
-        <v>0.26040000000000002</v>
+        <v>0.20181000000000004</v>
       </c>
       <c r="H62">
         <v>0.84455000000000002</v>
       </c>
       <c r="I62">
-        <v>0.29760000000000003</v>
+        <v>0.23064000000000004</v>
       </c>
       <c r="J62" t="s">
         <v>215</v>
@@ -7228,13 +7228,13 @@
         <v>3.75</v>
       </c>
       <c r="G63">
-        <v>0.23598749999999999</v>
+        <v>0.18289031250000001</v>
       </c>
       <c r="H63">
         <v>0.84455000000000002</v>
       </c>
       <c r="I63">
-        <v>0.2697</v>
+        <v>0.20901749999999999</v>
       </c>
       <c r="J63" t="s">
         <v>217</v>
@@ -7257,13 +7257,13 @@
         <v>3.75</v>
       </c>
       <c r="G64">
-        <v>0.23598749999999999</v>
+        <v>0.18289031250000001</v>
       </c>
       <c r="H64">
         <v>0.84455000000000002</v>
       </c>
       <c r="I64">
-        <v>0.2697</v>
+        <v>0.20901749999999999</v>
       </c>
       <c r="J64" t="s">
         <v>219</v>
@@ -7286,13 +7286,13 @@
         <v>3.75</v>
       </c>
       <c r="G65">
-        <v>0.22378125000000004</v>
+        <v>0.17343046875000001</v>
       </c>
       <c r="H65">
         <v>0.84455000000000002</v>
       </c>
       <c r="I65">
-        <v>0.25575000000000003</v>
+        <v>0.19820625000000003</v>
       </c>
       <c r="J65" t="s">
         <v>221</v>
@@ -7315,13 +7315,13 @@
         <v>3.75</v>
       </c>
       <c r="G66">
-        <v>0.26040000000000002</v>
+        <v>0.20181000000000004</v>
       </c>
       <c r="H66">
         <v>0.84455000000000002</v>
       </c>
       <c r="I66">
-        <v>0.29760000000000003</v>
+        <v>0.23064000000000004</v>
       </c>
       <c r="J66" t="s">
         <v>223</v>
@@ -7344,13 +7344,13 @@
         <v>3.75</v>
       </c>
       <c r="G67">
-        <v>0.26040000000000002</v>
+        <v>0.20181000000000004</v>
       </c>
       <c r="H67">
         <v>0.84455000000000002</v>
       </c>
       <c r="I67">
-        <v>0.29760000000000003</v>
+        <v>0.23064000000000004</v>
       </c>
       <c r="J67" t="s">
         <v>225</v>
@@ -7373,13 +7373,13 @@
         <v>3.75</v>
       </c>
       <c r="G68">
-        <v>0.21564375000000002</v>
+        <v>0.16712390625000001</v>
       </c>
       <c r="H68">
         <v>0.84455000000000002</v>
       </c>
       <c r="I68">
-        <v>0.24645000000000003</v>
+        <v>0.19099875000000002</v>
       </c>
       <c r="J68" t="s">
         <v>227</v>
@@ -7402,13 +7402,13 @@
         <v>3.75</v>
       </c>
       <c r="G69">
-        <v>0.21564375000000002</v>
+        <v>0.16712390625000001</v>
       </c>
       <c r="H69">
         <v>0.84455000000000002</v>
       </c>
       <c r="I69">
-        <v>0.24645000000000003</v>
+        <v>0.19099875000000002</v>
       </c>
       <c r="J69" t="s">
         <v>229</v>
@@ -7431,13 +7431,13 @@
         <v>3.75</v>
       </c>
       <c r="G70">
-        <v>0.2522625</v>
+        <v>0.19550343749999999</v>
       </c>
       <c r="H70">
         <v>0.84455000000000002</v>
       </c>
       <c r="I70">
-        <v>0.2883</v>
+        <v>0.22343249999999998</v>
       </c>
       <c r="J70" t="s">
         <v>231</v>
@@ -7460,13 +7460,13 @@
         <v>3.75</v>
       </c>
       <c r="G71">
-        <v>0.2522625</v>
+        <v>0.19550343749999999</v>
       </c>
       <c r="H71">
         <v>0.84455000000000002</v>
       </c>
       <c r="I71">
-        <v>0.2883</v>
+        <v>0.22343249999999998</v>
       </c>
       <c r="J71" t="s">
         <v>233</v>
@@ -7489,13 +7489,13 @@
         <v>3.75</v>
       </c>
       <c r="G72">
-        <v>0.2522625</v>
+        <v>0.19550343749999999</v>
       </c>
       <c r="H72">
         <v>0.84455000000000002</v>
       </c>
       <c r="I72">
-        <v>0.2883</v>
+        <v>0.22343249999999998</v>
       </c>
       <c r="J72" t="s">
         <v>235</v>
@@ -7518,13 +7518,13 @@
         <v>3.75</v>
       </c>
       <c r="G73">
-        <v>0.2522625</v>
+        <v>0.19550343749999999</v>
       </c>
       <c r="H73">
         <v>0.84455000000000002</v>
       </c>
       <c r="I73">
-        <v>0.2883</v>
+        <v>0.22343249999999998</v>
       </c>
       <c r="J73" t="s">
         <v>237</v>
@@ -7547,13 +7547,13 @@
         <v>3.75</v>
       </c>
       <c r="G74">
-        <v>0.23598749999999999</v>
+        <v>0.18289031250000001</v>
       </c>
       <c r="H74">
         <v>0.84455000000000002</v>
       </c>
       <c r="I74">
-        <v>0.2697</v>
+        <v>0.20901750000000002</v>
       </c>
       <c r="J74" t="s">
         <v>239</v>
@@ -7576,13 +7576,13 @@
         <v>3.75</v>
       </c>
       <c r="G75">
-        <v>0.23598749999999999</v>
+        <v>0.18289031250000001</v>
       </c>
       <c r="H75">
         <v>0.84455000000000002</v>
       </c>
       <c r="I75">
-        <v>0.2697</v>
+        <v>0.20901750000000002</v>
       </c>
       <c r="J75" t="s">
         <v>242</v>
@@ -7605,13 +7605,13 @@
         <v>3.75</v>
       </c>
       <c r="G76">
-        <v>0.21564375000000002</v>
+        <v>0.16712390625000001</v>
       </c>
       <c r="H76">
         <v>0.84455000000000002</v>
       </c>
       <c r="I76">
-        <v>0.24645000000000003</v>
+        <v>0.19099874999999999</v>
       </c>
       <c r="J76" t="s">
         <v>244</v>
@@ -7634,13 +7634,13 @@
         <v>3.75</v>
       </c>
       <c r="G77">
-        <v>0.23598749999999999</v>
+        <v>0.18289031250000001</v>
       </c>
       <c r="H77">
         <v>0.84455000000000002</v>
       </c>
       <c r="I77">
-        <v>0.2697</v>
+        <v>0.20901749999999999</v>
       </c>
       <c r="J77" t="s">
         <v>246</v>
@@ -7663,13 +7663,13 @@
         <v>3.75</v>
       </c>
       <c r="G78">
-        <v>0.23598749999999999</v>
+        <v>0.18289031250000001</v>
       </c>
       <c r="H78">
         <v>0.84455000000000002</v>
       </c>
       <c r="I78">
-        <v>0.2697</v>
+        <v>0.20901749999999999</v>
       </c>
       <c r="J78" t="s">
         <v>248</v>
@@ -7692,13 +7692,13 @@
         <v>3.75</v>
       </c>
       <c r="G79">
-        <v>0.23598749999999999</v>
+        <v>0.18289031250000001</v>
       </c>
       <c r="H79">
         <v>0.84455000000000002</v>
       </c>
       <c r="I79">
-        <v>0.2697</v>
+        <v>0.20901749999999999</v>
       </c>
       <c r="J79" t="s">
         <v>250</v>
@@ -7721,13 +7721,13 @@
         <v>3.75</v>
       </c>
       <c r="G80">
-        <v>0.23598749999999999</v>
+        <v>0.18289031250000001</v>
       </c>
       <c r="H80">
         <v>0.84455000000000002</v>
       </c>
       <c r="I80">
-        <v>0.2697</v>
+        <v>0.20901749999999999</v>
       </c>
       <c r="J80" t="s">
         <v>252</v>
@@ -7750,13 +7750,13 @@
         <v>3.75</v>
       </c>
       <c r="G81">
-        <v>0.23598749999999999</v>
+        <v>0.18289031250000001</v>
       </c>
       <c r="H81">
         <v>0.84455000000000002</v>
       </c>
       <c r="I81">
-        <v>0.2697</v>
+        <v>0.20901749999999999</v>
       </c>
       <c r="J81" t="s">
         <v>254</v>
@@ -7779,13 +7779,13 @@
         <v>3.75</v>
       </c>
       <c r="G82">
-        <v>0.23598749999999999</v>
+        <v>0.18289031250000001</v>
       </c>
       <c r="H82">
         <v>0.84455000000000002</v>
       </c>
       <c r="I82">
-        <v>0.2697</v>
+        <v>0.20901749999999999</v>
       </c>
       <c r="J82" t="s">
         <v>256</v>
@@ -7808,13 +7808,13 @@
         <v>3.75</v>
       </c>
       <c r="G83">
-        <v>0.22785</v>
+        <v>0.17658375000000004</v>
       </c>
       <c r="H83">
         <v>0.84455000000000002</v>
       </c>
       <c r="I83">
-        <v>0.26040000000000002</v>
+        <v>0.20181000000000002</v>
       </c>
       <c r="J83" t="s">
         <v>258</v>
@@ -7837,13 +7837,13 @@
         <v>3.75</v>
       </c>
       <c r="G84">
-        <v>0.22785</v>
+        <v>0.17658375000000004</v>
       </c>
       <c r="H84">
         <v>0.84455000000000002</v>
       </c>
       <c r="I84">
-        <v>0.26040000000000002</v>
+        <v>0.20181000000000002</v>
       </c>
       <c r="J84" t="s">
         <v>260</v>
@@ -7866,13 +7866,13 @@
         <v>3.75</v>
       </c>
       <c r="G85">
-        <v>0.2522625</v>
+        <v>0.19550343749999999</v>
       </c>
       <c r="H85">
         <v>0.84455000000000002</v>
       </c>
       <c r="I85">
-        <v>0.2883</v>
+        <v>0.22343250000000001</v>
       </c>
       <c r="J85" t="s">
         <v>262</v>
@@ -7895,13 +7895,13 @@
         <v>3.75</v>
       </c>
       <c r="G86">
-        <v>0.2522625</v>
+        <v>0.19550343749999999</v>
       </c>
       <c r="H86">
         <v>0.84455000000000002</v>
       </c>
       <c r="I86">
-        <v>0.2883</v>
+        <v>0.22343250000000001</v>
       </c>
       <c r="J86" t="s">
         <v>265</v>
@@ -7924,13 +7924,13 @@
         <v>3.75</v>
       </c>
       <c r="G87">
-        <v>0.2522625</v>
+        <v>0.19550343749999999</v>
       </c>
       <c r="H87">
         <v>0.84455000000000002</v>
       </c>
       <c r="I87">
-        <v>0.2883</v>
+        <v>0.22343250000000001</v>
       </c>
       <c r="J87" t="s">
         <v>267</v>
@@ -7953,13 +7953,13 @@
         <v>3.75</v>
       </c>
       <c r="G88">
-        <v>0.2522625</v>
+        <v>0.19550343749999999</v>
       </c>
       <c r="H88">
         <v>0.84455000000000002</v>
       </c>
       <c r="I88">
-        <v>0.2883</v>
+        <v>0.22343250000000001</v>
       </c>
       <c r="J88" t="s">
         <v>269</v>
@@ -7982,13 +7982,13 @@
         <v>3.75</v>
       </c>
       <c r="G89">
-        <v>0.2522625</v>
+        <v>0.19550343749999999</v>
       </c>
       <c r="H89">
         <v>0.84455000000000002</v>
       </c>
       <c r="I89">
-        <v>0.2883</v>
+        <v>0.22343250000000001</v>
       </c>
       <c r="J89" t="s">
         <v>271</v>
@@ -8011,13 +8011,13 @@
         <v>3.75</v>
       </c>
       <c r="G90">
-        <v>0.23598749999999999</v>
+        <v>0.18289031250000001</v>
       </c>
       <c r="H90">
         <v>0.84455000000000002</v>
       </c>
       <c r="I90">
-        <v>0.2697</v>
+        <v>0.20901749999999999</v>
       </c>
       <c r="J90" t="s">
         <v>273</v>
@@ -8040,13 +8040,13 @@
         <v>3.75</v>
       </c>
       <c r="G91">
-        <v>0.23598749999999999</v>
+        <v>0.18289031250000001</v>
       </c>
       <c r="H91">
         <v>0.84455000000000002</v>
       </c>
       <c r="I91">
-        <v>0.2697</v>
+        <v>0.20901749999999999</v>
       </c>
       <c r="J91" t="s">
         <v>275</v>
@@ -8069,13 +8069,13 @@
         <v>3.75</v>
       </c>
       <c r="G92">
-        <v>0.23598749999999999</v>
+        <v>0.18289031250000001</v>
       </c>
       <c r="H92">
         <v>0.84455000000000002</v>
       </c>
       <c r="I92">
-        <v>0.2697</v>
+        <v>0.20901750000000002</v>
       </c>
       <c r="J92" t="s">
         <v>277</v>
@@ -8098,13 +8098,13 @@
         <v>3.75</v>
       </c>
       <c r="G93">
-        <v>0.23598749999999999</v>
+        <v>0.18289031250000001</v>
       </c>
       <c r="H93">
         <v>0.84455000000000002</v>
       </c>
       <c r="I93">
-        <v>0.2697</v>
+        <v>0.20901750000000002</v>
       </c>
       <c r="J93" t="s">
         <v>279</v>
@@ -8127,13 +8127,13 @@
         <v>3.75</v>
       </c>
       <c r="G94">
-        <v>0.23598749999999999</v>
+        <v>0.18289031250000001</v>
       </c>
       <c r="H94">
         <v>0.84455000000000002</v>
       </c>
       <c r="I94">
-        <v>0.2697</v>
+        <v>0.20901749999999999</v>
       </c>
       <c r="J94" t="s">
         <v>281</v>
@@ -8156,13 +8156,13 @@
         <v>3.75</v>
       </c>
       <c r="G95">
-        <v>0.23598749999999999</v>
+        <v>0.18289031250000001</v>
       </c>
       <c r="H95">
         <v>0.84455000000000002</v>
       </c>
       <c r="I95">
-        <v>0.2697</v>
+        <v>0.20901749999999999</v>
       </c>
       <c r="J95" t="s">
         <v>285</v>
@@ -8185,13 +8185,13 @@
         <v>3.75</v>
       </c>
       <c r="G96">
-        <v>0.23598749999999999</v>
+        <v>0.18289031250000001</v>
       </c>
       <c r="H96">
         <v>0.84455000000000002</v>
       </c>
       <c r="I96">
-        <v>0.2697</v>
+        <v>0.20901749999999999</v>
       </c>
       <c r="J96" t="s">
         <v>287</v>
@@ -8214,13 +8214,13 @@
         <v>3.75</v>
       </c>
       <c r="G97">
-        <v>0.21564375000000002</v>
+        <v>0.16712390625000001</v>
       </c>
       <c r="H97">
         <v>0.84455000000000002</v>
       </c>
       <c r="I97">
-        <v>0.24645000000000003</v>
+        <v>0.19099874999999999</v>
       </c>
       <c r="J97" t="s">
         <v>289</v>
@@ -8243,13 +8243,13 @@
         <v>3.75</v>
       </c>
       <c r="G98">
-        <v>0.21564375000000002</v>
+        <v>0.16712390625000001</v>
       </c>
       <c r="H98">
         <v>0.84455000000000002</v>
       </c>
       <c r="I98">
-        <v>0.24645000000000003</v>
+        <v>0.19099874999999999</v>
       </c>
       <c r="J98" t="s">
         <v>291</v>
@@ -8272,13 +8272,13 @@
         <v>3.75</v>
       </c>
       <c r="G99">
-        <v>0.21564375000000002</v>
+        <v>0.16712390625000001</v>
       </c>
       <c r="H99">
         <v>0.84455000000000002</v>
       </c>
       <c r="I99">
-        <v>0.24645000000000003</v>
+        <v>0.19099874999999999</v>
       </c>
       <c r="J99" t="s">
         <v>293</v>
@@ -8301,13 +8301,13 @@
         <v>3.75</v>
       </c>
       <c r="G100">
-        <v>0.23598749999999999</v>
+        <v>0.18289031250000001</v>
       </c>
       <c r="H100">
         <v>0.84455000000000002</v>
       </c>
       <c r="I100">
-        <v>0.2697</v>
+        <v>0.20901749999999999</v>
       </c>
       <c r="J100" t="s">
         <v>295</v>
@@ -8330,13 +8330,13 @@
         <v>3.75</v>
       </c>
       <c r="G101">
-        <v>0.23598749999999999</v>
+        <v>0.18289031250000001</v>
       </c>
       <c r="H101">
         <v>0.84455000000000002</v>
       </c>
       <c r="I101">
-        <v>0.2697</v>
+        <v>0.20901749999999999</v>
       </c>
       <c r="J101" t="s">
         <v>297</v>
@@ -8359,13 +8359,13 @@
         <v>3.75</v>
       </c>
       <c r="G102">
-        <v>0.26040000000000002</v>
+        <v>0.20181000000000002</v>
       </c>
       <c r="H102">
         <v>0.84455000000000002</v>
       </c>
       <c r="I102">
-        <v>0.29760000000000003</v>
+        <v>0.23064000000000001</v>
       </c>
       <c r="J102" t="s">
         <v>299</v>
@@ -8388,13 +8388,13 @@
         <v>3.75</v>
       </c>
       <c r="G103">
-        <v>0.26040000000000002</v>
+        <v>0.20181000000000002</v>
       </c>
       <c r="H103">
         <v>0.84455000000000002</v>
       </c>
       <c r="I103">
-        <v>0.29760000000000003</v>
+        <v>0.23064000000000001</v>
       </c>
       <c r="J103" t="s">
         <v>301</v>
@@ -8417,13 +8417,13 @@
         <v>3.75</v>
       </c>
       <c r="G104">
-        <v>0.26040000000000002</v>
+        <v>0.20181000000000002</v>
       </c>
       <c r="H104">
         <v>0.84455000000000002</v>
       </c>
       <c r="I104">
-        <v>0.29760000000000003</v>
+        <v>0.23064000000000001</v>
       </c>
       <c r="J104" t="s">
         <v>303</v>
@@ -8446,13 +8446,13 @@
         <v>3.75</v>
       </c>
       <c r="G105">
-        <v>0.26040000000000002</v>
+        <v>0.20181000000000002</v>
       </c>
       <c r="H105">
         <v>0.84455000000000002</v>
       </c>
       <c r="I105">
-        <v>0.29760000000000003</v>
+        <v>0.23064000000000001</v>
       </c>
       <c r="J105" t="s">
         <v>305</v>
@@ -8475,13 +8475,13 @@
         <v>3.75</v>
       </c>
       <c r="G106">
-        <v>0.26853750000000004</v>
+        <v>0.20811656249999999</v>
       </c>
       <c r="H106">
         <v>0.84455000000000002</v>
       </c>
       <c r="I106">
-        <v>0.30690000000000001</v>
+        <v>0.23784749999999999</v>
       </c>
       <c r="J106" t="s">
         <v>307</v>
@@ -8504,13 +8504,13 @@
         <v>3.75</v>
       </c>
       <c r="G107">
-        <v>0.26853750000000004</v>
+        <v>0.20811656249999999</v>
       </c>
       <c r="H107">
         <v>0.84455000000000002</v>
       </c>
       <c r="I107">
-        <v>0.30690000000000001</v>
+        <v>0.23784749999999999</v>
       </c>
       <c r="J107" t="s">
         <v>309</v>
@@ -8533,13 +8533,13 @@
         <v>3.75</v>
       </c>
       <c r="G108">
-        <v>0.26853750000000004</v>
+        <v>0.20811656249999999</v>
       </c>
       <c r="H108">
         <v>0.84455000000000002</v>
       </c>
       <c r="I108">
-        <v>0.30690000000000001</v>
+        <v>0.23784749999999999</v>
       </c>
       <c r="J108" t="s">
         <v>311</v>
@@ -8562,13 +8562,13 @@
         <v>3.75</v>
       </c>
       <c r="G109">
-        <v>0.26853750000000004</v>
+        <v>0.20811656249999999</v>
       </c>
       <c r="H109">
         <v>0.84455000000000002</v>
       </c>
       <c r="I109">
-        <v>0.30690000000000001</v>
+        <v>0.23784749999999999</v>
       </c>
       <c r="J109" t="s">
         <v>313</v>
@@ -8591,13 +8591,13 @@
         <v>3.75</v>
       </c>
       <c r="G110">
-        <v>0.26853750000000004</v>
+        <v>0.20811656249999999</v>
       </c>
       <c r="H110">
         <v>0.84455000000000002</v>
       </c>
       <c r="I110">
-        <v>0.30690000000000001</v>
+        <v>0.23784749999999999</v>
       </c>
       <c r="J110" t="s">
         <v>315</v>
@@ -8620,13 +8620,13 @@
         <v>3.75</v>
       </c>
       <c r="G111">
-        <v>0.26853750000000004</v>
+        <v>0.20811656249999999</v>
       </c>
       <c r="H111">
         <v>0.84455000000000002</v>
       </c>
       <c r="I111">
-        <v>0.30690000000000001</v>
+        <v>0.23784749999999999</v>
       </c>
       <c r="J111" t="s">
         <v>317</v>
@@ -8649,13 +8649,13 @@
         <v>3.75</v>
       </c>
       <c r="G112">
-        <v>0.28074374999999996</v>
+        <v>0.21757640624999997</v>
       </c>
       <c r="H112">
         <v>0.84455000000000002</v>
       </c>
       <c r="I112">
-        <v>0.32084999999999997</v>
+        <v>0.24865874999999998</v>
       </c>
       <c r="J112" t="s">
         <v>319</v>
@@ -8678,13 +8678,13 @@
         <v>3.75</v>
       </c>
       <c r="G113">
-        <v>0.29701875</v>
+        <v>0.23018953125000002</v>
       </c>
       <c r="H113">
         <v>0.84455000000000002</v>
       </c>
       <c r="I113">
-        <v>0.33945000000000003</v>
+        <v>0.26307375000000005</v>
       </c>
       <c r="J113" t="s">
         <v>321</v>
@@ -8707,13 +8707,13 @@
         <v>3.75</v>
       </c>
       <c r="G114">
-        <v>0.28074374999999996</v>
+        <v>0.21757640624999997</v>
       </c>
       <c r="H114">
         <v>0.84455000000000002</v>
       </c>
       <c r="I114">
-        <v>0.32084999999999997</v>
+        <v>0.24865874999999998</v>
       </c>
       <c r="J114" t="s">
         <v>323</v>
@@ -8736,13 +8736,13 @@
         <v>3.75</v>
       </c>
       <c r="G115">
-        <v>0.29701875</v>
+        <v>0.23018953125000002</v>
       </c>
       <c r="H115">
         <v>0.84455000000000002</v>
       </c>
       <c r="I115">
-        <v>0.33945000000000003</v>
+        <v>0.26307375000000005</v>
       </c>
       <c r="J115" t="s">
         <v>327</v>
@@ -8765,13 +8765,13 @@
         <v>3.75</v>
       </c>
       <c r="G116">
-        <v>0.29701875</v>
+        <v>0.23018953125000002</v>
       </c>
       <c r="H116">
         <v>0.84455000000000002</v>
       </c>
       <c r="I116">
-        <v>0.33945000000000003</v>
+        <v>0.26307375000000005</v>
       </c>
       <c r="J116" t="s">
         <v>329</v>
@@ -8794,13 +8794,13 @@
         <v>3.75</v>
       </c>
       <c r="G117">
-        <v>0.29701875</v>
+        <v>0.23018953125000002</v>
       </c>
       <c r="H117">
         <v>0.84455000000000002</v>
       </c>
       <c r="I117">
-        <v>0.33945000000000003</v>
+        <v>0.26307375000000005</v>
       </c>
       <c r="J117" t="s">
         <v>331</v>
@@ -8823,13 +8823,13 @@
         <v>3.75</v>
       </c>
       <c r="G118">
-        <v>0.29701875</v>
+        <v>0.23018953125000002</v>
       </c>
       <c r="H118">
         <v>0.84455000000000002</v>
       </c>
       <c r="I118">
-        <v>0.33945000000000003</v>
+        <v>0.26307375000000005</v>
       </c>
       <c r="J118" t="s">
         <v>333</v>
@@ -8852,13 +8852,13 @@
         <v>3.75</v>
       </c>
       <c r="G119">
-        <v>0.28982625000000001</v>
+        <v>0.22461534375000003</v>
       </c>
       <c r="H119">
         <v>0.84455000000000002</v>
       </c>
       <c r="I119">
-        <v>0.33123000000000002</v>
+        <v>0.25670325000000005</v>
       </c>
       <c r="J119" t="s">
         <v>645</v>
@@ -8881,13 +8881,13 @@
         <v>3.75</v>
       </c>
       <c r="G120">
-        <v>0.28982625000000001</v>
+        <v>0.22461534375000003</v>
       </c>
       <c r="H120">
         <v>0.84455000000000002</v>
       </c>
       <c r="I120">
-        <v>0.33123000000000002</v>
+        <v>0.25670325000000005</v>
       </c>
       <c r="J120" t="s">
         <v>647</v>
@@ -8910,13 +8910,13 @@
         <v>3.75</v>
       </c>
       <c r="G121">
-        <v>0.28982625000000001</v>
+        <v>0.22461534375000003</v>
       </c>
       <c r="H121">
         <v>0.84455000000000002</v>
       </c>
       <c r="I121">
-        <v>0.33123000000000002</v>
+        <v>0.25670325000000005</v>
       </c>
       <c r="J121" t="s">
         <v>648</v>
@@ -8939,13 +8939,13 @@
         <v>3.75</v>
       </c>
       <c r="G122">
-        <v>0.28982625000000001</v>
+        <v>0.22461534375000003</v>
       </c>
       <c r="H122">
         <v>0.84455000000000002</v>
       </c>
       <c r="I122">
-        <v>0.33123000000000002</v>
+        <v>0.25670325000000005</v>
       </c>
       <c r="J122" t="s">
         <v>649</v>
@@ -8968,13 +8968,13 @@
         <v>3.75</v>
       </c>
       <c r="G123">
-        <v>0.28982625000000001</v>
+        <v>0.22461534375000003</v>
       </c>
       <c r="H123">
         <v>0.84455000000000002</v>
       </c>
       <c r="I123">
-        <v>0.33123000000000002</v>
+        <v>0.25670325000000005</v>
       </c>
       <c r="J123" t="s">
         <v>651</v>
@@ -8997,13 +8997,13 @@
         <v>3.75</v>
       </c>
       <c r="G124">
-        <v>0.28982625000000001</v>
+        <v>0.22461534375000003</v>
       </c>
       <c r="H124">
         <v>0.84455000000000002</v>
       </c>
       <c r="I124">
-        <v>0.33123000000000002</v>
+        <v>0.25670325000000005</v>
       </c>
       <c r="J124" t="s">
         <v>653</v>
@@ -9026,13 +9026,13 @@
         <v>3.75</v>
       </c>
       <c r="G125">
-        <v>0.28982625000000001</v>
+        <v>0.22461534375000003</v>
       </c>
       <c r="H125">
         <v>0.84455000000000002</v>
       </c>
       <c r="I125">
-        <v>0.33123000000000002</v>
+        <v>0.25670325000000005</v>
       </c>
       <c r="J125" t="s">
         <v>655</v>
@@ -9055,13 +9055,13 @@
         <v>3.75</v>
       </c>
       <c r="G126">
-        <v>0.28982625000000006</v>
+        <v>0.22461534375000003</v>
       </c>
       <c r="H126">
         <v>0.84455000000000002</v>
       </c>
       <c r="I126">
-        <v>0.33123000000000008</v>
+        <v>0.25670325000000005</v>
       </c>
       <c r="J126" t="s">
         <v>657</v>
@@ -9084,13 +9084,13 @@
         <v>3.75</v>
       </c>
       <c r="G127">
-        <v>0.28982625000000001</v>
+        <v>0.22461534375000003</v>
       </c>
       <c r="H127">
         <v>0.84455000000000002</v>
       </c>
       <c r="I127">
-        <v>0.33123000000000002</v>
+        <v>0.25670325000000005</v>
       </c>
       <c r="J127" t="s">
         <v>658</v>
@@ -9113,13 +9113,13 @@
         <v>3.75</v>
       </c>
       <c r="G128">
-        <v>0.28982625000000001</v>
+        <v>0.22461534375000003</v>
       </c>
       <c r="H128">
         <v>0.84455000000000002</v>
       </c>
       <c r="I128">
-        <v>0.33123000000000002</v>
+        <v>0.25670325000000005</v>
       </c>
       <c r="J128" t="s">
         <v>660</v>
@@ -9142,13 +9142,13 @@
         <v>3.75</v>
       </c>
       <c r="G129">
-        <v>0.28982625000000001</v>
+        <v>0.22461534375000003</v>
       </c>
       <c r="H129">
         <v>0.84455000000000002</v>
       </c>
       <c r="I129">
-        <v>0.33123000000000002</v>
+        <v>0.25670325000000005</v>
       </c>
       <c r="J129" t="s">
         <v>661</v>
@@ -9171,13 +9171,13 @@
         <v>3.75</v>
       </c>
       <c r="G130">
-        <v>0.28982625000000006</v>
+        <v>0.22461534375000003</v>
       </c>
       <c r="H130">
         <v>0.84455000000000002</v>
       </c>
       <c r="I130">
-        <v>0.33123000000000008</v>
+        <v>0.25670325000000005</v>
       </c>
       <c r="J130" t="s">
         <v>663</v>
@@ -9200,13 +9200,13 @@
         <v>3.75</v>
       </c>
       <c r="G131">
-        <v>0.28982625000000001</v>
+        <v>0.22461534375000003</v>
       </c>
       <c r="H131">
         <v>0.84455000000000002</v>
       </c>
       <c r="I131">
-        <v>0.33123000000000002</v>
+        <v>0.25670325000000005</v>
       </c>
       <c r="J131" t="s">
         <v>664</v>
@@ -9229,13 +9229,13 @@
         <v>3.75</v>
       </c>
       <c r="G132">
-        <v>0.28982625000000001</v>
+        <v>0.22461534375000003</v>
       </c>
       <c r="H132">
         <v>0.84455000000000002</v>
       </c>
       <c r="I132">
-        <v>0.33123000000000002</v>
+        <v>0.25670325000000005</v>
       </c>
       <c r="J132" t="s">
         <v>665</v>
@@ -9247,7 +9247,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7F7503C0-6058-49E7-B7F3-DA5C2A106C3D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{104B0AB3-4F22-4C25-B22D-DE1F1431BB85}">
   <dimension ref="A1:H32"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -9562,10 +9562,10 @@
         <v>0.11</v>
       </c>
       <c r="E27">
-        <v>0.3</v>
+        <v>0.21</v>
       </c>
       <c r="F27">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="G27">
         <v>0.1</v>
@@ -9582,7 +9582,7 @@
         <v>98</v>
       </c>
       <c r="E28">
-        <v>0.41</v>
+        <v>0.28999999999999998</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.45">
@@ -9599,13 +9599,13 @@
         <v>0.35</v>
       </c>
       <c r="E29">
-        <v>0.45</v>
+        <v>0.35</v>
       </c>
       <c r="F29">
-        <v>390.1</v>
+        <v>503.3</v>
       </c>
       <c r="G29">
-        <v>301.3</v>
+        <v>388.8</v>
       </c>
       <c r="H29">
         <v>370.2</v>
@@ -9684,7 +9684,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2751C394-92FC-4214-B89C-4F0E290C9EB6}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8DDA9136-C63A-4C22-8EBD-519B99CA8837}">
   <dimension ref="A1:Y197"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -10775,7 +10775,7 @@
         <v>9.1199999999999992</v>
       </c>
       <c r="P27">
-        <v>0.29760000000000003</v>
+        <v>0.20832000000000001</v>
       </c>
       <c r="R27">
         <v>38</v>
@@ -10846,7 +10846,7 @@
         <v>8.36</v>
       </c>
       <c r="P28">
-        <v>0.30690000000000001</v>
+        <v>0.21483000000000002</v>
       </c>
       <c r="R28">
         <v>38</v>
@@ -10920,7 +10920,7 @@
         <v>5.2249999999999996</v>
       </c>
       <c r="P29">
-        <v>0.40455000000000002</v>
+        <v>0.28318500000000002</v>
       </c>
       <c r="R29">
         <v>48</v>
@@ -10994,7 +10994,7 @@
         <v>5.2249999999999996</v>
       </c>
       <c r="P30">
-        <v>0.41385000000000005</v>
+        <v>0.28969500000000004</v>
       </c>
       <c r="R30">
         <v>48</v>
@@ -11050,7 +11050,7 @@
         <v>6.6765601135218886E-2</v>
       </c>
       <c r="P31">
-        <v>0.33123000000000002</v>
+        <v>0.25670325000000005</v>
       </c>
     </row>
     <row r="32" spans="1:25" x14ac:dyDescent="0.45">
@@ -11082,7 +11082,7 @@
         <v>0.17331237294683902</v>
       </c>
       <c r="P32">
-        <v>0.33123000000000002</v>
+        <v>0.25670325000000005</v>
       </c>
     </row>
     <row r="33" spans="1:25" x14ac:dyDescent="0.45">
@@ -11114,7 +11114,7 @@
         <v>6.9547501182519678E-2</v>
       </c>
       <c r="P33">
-        <v>0.33123000000000002</v>
+        <v>0.25670325000000005</v>
       </c>
     </row>
     <row r="34" spans="1:25" x14ac:dyDescent="0.45">
@@ -11146,7 +11146,7 @@
         <v>4.1728500709511805E-2</v>
       </c>
       <c r="P34">
-        <v>0.33123000000000002</v>
+        <v>0.25670325000000005</v>
       </c>
     </row>
     <row r="35" spans="1:25" x14ac:dyDescent="0.45">
@@ -11196,7 +11196,7 @@
         <v>2.8499999999999996</v>
       </c>
       <c r="P35">
-        <v>0.50685000000000002</v>
+        <v>0.39280875000000004</v>
       </c>
       <c r="R35">
         <v>55</v>
@@ -11270,7 +11270,7 @@
         <v>2.8499999999999996</v>
       </c>
       <c r="P36">
-        <v>0.53939999999999999</v>
+        <v>0.41803500000000005</v>
       </c>
       <c r="R36">
         <v>55</v>
@@ -11344,7 +11344,7 @@
         <v>2.8499999999999996</v>
       </c>
       <c r="P37">
-        <v>0.53939999999999999</v>
+        <v>0.41803499999999999</v>
       </c>
       <c r="R37">
         <v>55</v>
@@ -11418,7 +11418,7 @@
         <v>2.8499999999999996</v>
       </c>
       <c r="P38">
-        <v>0.53939999999999999</v>
+        <v>0.41803500000000005</v>
       </c>
       <c r="R38">
         <v>55</v>
@@ -11489,7 +11489,7 @@
         <v>2.8499999999999996</v>
       </c>
       <c r="P39">
-        <v>0.55800000000000005</v>
+        <v>0.43245000000000006</v>
       </c>
       <c r="R39">
         <v>55</v>
@@ -11560,7 +11560,7 @@
         <v>2.8499999999999996</v>
       </c>
       <c r="P40">
-        <v>0.48825000000000007</v>
+        <v>0.37839375000000008</v>
       </c>
       <c r="R40">
         <v>55</v>
@@ -11631,7 +11631,7 @@
         <v>2.8499999999999996</v>
       </c>
       <c r="P41">
-        <v>0.41850000000000009</v>
+        <v>0.32433750000000006</v>
       </c>
       <c r="R41">
         <v>55</v>
@@ -11702,7 +11702,7 @@
         <v>2.8499999999999996</v>
       </c>
       <c r="P42">
-        <v>0.50685000000000002</v>
+        <v>0.39280875000000004</v>
       </c>
       <c r="R42">
         <v>55</v>
@@ -11773,7 +11773,7 @@
         <v>2.8499999999999996</v>
       </c>
       <c r="P43">
-        <v>0.50685000000000002</v>
+        <v>0.39280875000000004</v>
       </c>
       <c r="R43">
         <v>55</v>
@@ -11844,7 +11844,7 @@
         <v>2.8499999999999996</v>
       </c>
       <c r="P44">
-        <v>0.50685000000000002</v>
+        <v>0.39280875000000004</v>
       </c>
       <c r="R44">
         <v>55</v>
@@ -11915,7 +11915,7 @@
         <v>2.8499999999999996</v>
       </c>
       <c r="P45">
-        <v>0.53939999999999999</v>
+        <v>0.41803499999999999</v>
       </c>
       <c r="R45">
         <v>55</v>
@@ -11986,7 +11986,7 @@
         <v>2.8499999999999996</v>
       </c>
       <c r="P46">
-        <v>0.53939999999999999</v>
+        <v>0.41803499999999999</v>
       </c>
       <c r="R46">
         <v>55</v>
@@ -12057,7 +12057,7 @@
         <v>2.8499999999999996</v>
       </c>
       <c r="P47">
-        <v>0.53939999999999999</v>
+        <v>0.41803499999999999</v>
       </c>
       <c r="R47">
         <v>55</v>
@@ -12128,7 +12128,7 @@
         <v>2.8499999999999996</v>
       </c>
       <c r="P48">
-        <v>0.53939999999999999</v>
+        <v>0.41803499999999999</v>
       </c>
       <c r="R48">
         <v>55</v>
@@ -12199,7 +12199,7 @@
         <v>2.8499999999999996</v>
       </c>
       <c r="P49">
-        <v>0.55800000000000005</v>
+        <v>0.43245000000000006</v>
       </c>
       <c r="R49">
         <v>55</v>
@@ -12273,7 +12273,7 @@
         <v>2.8499999999999996</v>
       </c>
       <c r="P50">
-        <v>0.53939999999999999</v>
+        <v>0.41803499999999999</v>
       </c>
       <c r="R50">
         <v>55</v>
@@ -12344,7 +12344,7 @@
         <v>2.8499999999999996</v>
       </c>
       <c r="P51">
-        <v>0.55800000000000005</v>
+        <v>0.43245000000000006</v>
       </c>
       <c r="R51">
         <v>55</v>
@@ -12415,7 +12415,7 @@
         <v>2.8499999999999996</v>
       </c>
       <c r="P52">
-        <v>0.55800000000000005</v>
+        <v>0.43245000000000006</v>
       </c>
       <c r="R52">
         <v>55</v>
@@ -12486,7 +12486,7 @@
         <v>2.8499999999999996</v>
       </c>
       <c r="P53">
-        <v>0.55800000000000005</v>
+        <v>0.43245000000000006</v>
       </c>
       <c r="R53">
         <v>55</v>
@@ -12560,7 +12560,7 @@
         <v>2.8499999999999996</v>
       </c>
       <c r="P54">
-        <v>0.50685000000000002</v>
+        <v>0.39280875000000004</v>
       </c>
       <c r="R54">
         <v>55</v>
@@ -12634,7 +12634,7 @@
         <v>2.8499999999999996</v>
       </c>
       <c r="P55">
-        <v>0.53939999999999999</v>
+        <v>0.41803499999999993</v>
       </c>
       <c r="R55">
         <v>55</v>
@@ -12708,7 +12708,7 @@
         <v>2.8499999999999996</v>
       </c>
       <c r="P56">
-        <v>0.53939999999999999</v>
+        <v>0.41803499999999993</v>
       </c>
       <c r="R56">
         <v>55</v>
@@ -12782,7 +12782,7 @@
         <v>2.85</v>
       </c>
       <c r="P57">
-        <v>0.53939999999999999</v>
+        <v>0.41803499999999999</v>
       </c>
       <c r="R57">
         <v>55</v>
@@ -12856,7 +12856,7 @@
         <v>2.85</v>
       </c>
       <c r="P58">
-        <v>0.53939999999999999</v>
+        <v>0.41803499999999999</v>
       </c>
       <c r="R58">
         <v>55</v>
@@ -12930,7 +12930,7 @@
         <v>2.8499999999999996</v>
       </c>
       <c r="P59">
-        <v>0.50685000000000002</v>
+        <v>0.39280875000000004</v>
       </c>
       <c r="R59">
         <v>55</v>
@@ -13004,7 +13004,7 @@
         <v>2.8499999999999996</v>
       </c>
       <c r="P60">
-        <v>0.50685000000000002</v>
+        <v>0.39280875000000004</v>
       </c>
       <c r="R60">
         <v>55</v>
@@ -13075,7 +13075,7 @@
         <v>2.8499999999999996</v>
       </c>
       <c r="P61">
-        <v>0.50685000000000002</v>
+        <v>0.39280875000000004</v>
       </c>
       <c r="R61">
         <v>55</v>
@@ -13146,7 +13146,7 @@
         <v>2.8499999999999996</v>
       </c>
       <c r="P62">
-        <v>0.50685000000000002</v>
+        <v>0.39280875000000004</v>
       </c>
       <c r="R62">
         <v>55</v>
@@ -13217,7 +13217,7 @@
         <v>2.8499999999999996</v>
       </c>
       <c r="P63">
-        <v>0.55800000000000005</v>
+        <v>0.43245000000000006</v>
       </c>
       <c r="R63">
         <v>55</v>
@@ -13288,7 +13288,7 @@
         <v>2.8499999999999996</v>
       </c>
       <c r="P64">
-        <v>0.37200000000000005</v>
+        <v>0.28830000000000006</v>
       </c>
       <c r="R64">
         <v>55</v>
@@ -13359,7 +13359,7 @@
         <v>2.8499999999999992</v>
       </c>
       <c r="P65">
-        <v>0.53939999999999999</v>
+        <v>0.41803499999999999</v>
       </c>
       <c r="R65">
         <v>55</v>
@@ -13430,7 +13430,7 @@
         <v>2.8499999999999996</v>
       </c>
       <c r="P66">
-        <v>0.50685000000000002</v>
+        <v>0.39280875000000004</v>
       </c>
       <c r="R66">
         <v>55</v>
@@ -13501,7 +13501,7 @@
         <v>2.8499999999999996</v>
       </c>
       <c r="P67">
-        <v>0.50685000000000002</v>
+        <v>0.39280875000000004</v>
       </c>
       <c r="R67">
         <v>55</v>
@@ -13572,7 +13572,7 @@
         <v>2.8499999999999996</v>
       </c>
       <c r="P68">
-        <v>0.55800000000000005</v>
+        <v>0.43245000000000006</v>
       </c>
       <c r="R68">
         <v>55</v>
@@ -13646,7 +13646,7 @@
         <v>2.8499999999999996</v>
       </c>
       <c r="P69">
-        <v>0.50685000000000002</v>
+        <v>0.3928087500000001</v>
       </c>
       <c r="R69">
         <v>55</v>
@@ -13717,7 +13717,7 @@
         <v>4.18</v>
       </c>
       <c r="P70">
-        <v>0.21390000000000001</v>
+        <v>0.16577250000000002</v>
       </c>
       <c r="R70">
         <v>30</v>
@@ -13788,7 +13788,7 @@
         <v>4.18</v>
       </c>
       <c r="P71">
-        <v>0.21390000000000001</v>
+        <v>0.16577250000000002</v>
       </c>
       <c r="R71">
         <v>30</v>
@@ -13859,7 +13859,7 @@
         <v>4.18</v>
       </c>
       <c r="P72">
-        <v>0.24645000000000006</v>
+        <v>0.19099875000000002</v>
       </c>
       <c r="R72">
         <v>30</v>
@@ -13930,7 +13930,7 @@
         <v>4.18</v>
       </c>
       <c r="P73">
-        <v>0.24645000000000006</v>
+        <v>0.19099875000000002</v>
       </c>
       <c r="R73">
         <v>30</v>
@@ -14001,7 +14001,7 @@
         <v>4.18</v>
       </c>
       <c r="P74">
-        <v>0.24645000000000006</v>
+        <v>0.19099875000000002</v>
       </c>
       <c r="R74">
         <v>30</v>
@@ -14072,7 +14072,7 @@
         <v>4.18</v>
       </c>
       <c r="P75">
-        <v>0.24645000000000006</v>
+        <v>0.19099875000000002</v>
       </c>
       <c r="R75">
         <v>30</v>
@@ -14143,7 +14143,7 @@
         <v>4.18</v>
       </c>
       <c r="P76">
-        <v>0.24645000000000006</v>
+        <v>0.19099875000000002</v>
       </c>
       <c r="R76">
         <v>30</v>
@@ -14214,7 +14214,7 @@
         <v>4.18</v>
       </c>
       <c r="P77">
-        <v>0.24645000000000006</v>
+        <v>0.19099875000000002</v>
       </c>
       <c r="R77">
         <v>30</v>
@@ -14285,7 +14285,7 @@
         <v>4.18</v>
       </c>
       <c r="P78">
-        <v>0.2697</v>
+        <v>0.20901749999999999</v>
       </c>
       <c r="R78">
         <v>30</v>
@@ -14356,7 +14356,7 @@
         <v>4.18</v>
       </c>
       <c r="P79">
-        <v>0.2697</v>
+        <v>0.20901749999999999</v>
       </c>
       <c r="R79">
         <v>30</v>
@@ -14427,7 +14427,7 @@
         <v>4.18</v>
       </c>
       <c r="P80">
-        <v>0.2697</v>
+        <v>0.20901749999999999</v>
       </c>
       <c r="R80">
         <v>30</v>
@@ -14498,7 +14498,7 @@
         <v>4.18</v>
       </c>
       <c r="P81">
-        <v>0.2697</v>
+        <v>0.20901749999999999</v>
       </c>
       <c r="R81">
         <v>35</v>
@@ -14569,7 +14569,7 @@
         <v>4.18</v>
       </c>
       <c r="P82">
-        <v>0.2697</v>
+        <v>0.20901749999999999</v>
       </c>
       <c r="R82">
         <v>35</v>
@@ -14640,7 +14640,7 @@
         <v>4.18</v>
       </c>
       <c r="P83">
-        <v>0.2697</v>
+        <v>0.20901749999999999</v>
       </c>
       <c r="R83">
         <v>35</v>
@@ -14711,7 +14711,7 @@
         <v>4.18</v>
       </c>
       <c r="P84">
-        <v>0.2697</v>
+        <v>0.20901749999999999</v>
       </c>
       <c r="R84">
         <v>35</v>
@@ -14782,7 +14782,7 @@
         <v>4.18</v>
       </c>
       <c r="P85">
-        <v>0.29760000000000003</v>
+        <v>0.23064000000000004</v>
       </c>
       <c r="R85">
         <v>35</v>
@@ -14853,7 +14853,7 @@
         <v>4.18</v>
       </c>
       <c r="P86">
-        <v>0.29760000000000003</v>
+        <v>0.23064000000000004</v>
       </c>
       <c r="R86">
         <v>35</v>
@@ -14924,7 +14924,7 @@
         <v>4.18</v>
       </c>
       <c r="P87">
-        <v>0.29760000000000003</v>
+        <v>0.23064000000000004</v>
       </c>
       <c r="R87">
         <v>35</v>
@@ -14995,7 +14995,7 @@
         <v>4.18</v>
       </c>
       <c r="P88">
-        <v>0.2697</v>
+        <v>0.20901749999999999</v>
       </c>
       <c r="R88">
         <v>30</v>
@@ -15066,7 +15066,7 @@
         <v>4.18</v>
       </c>
       <c r="P89">
-        <v>0.2697</v>
+        <v>0.20901749999999999</v>
       </c>
       <c r="R89">
         <v>30</v>
@@ -15137,7 +15137,7 @@
         <v>3.7999999999999994</v>
       </c>
       <c r="P90">
-        <v>0.25575000000000003</v>
+        <v>0.19820625000000003</v>
       </c>
       <c r="R90">
         <v>35</v>
@@ -15208,7 +15208,7 @@
         <v>4.18</v>
       </c>
       <c r="P91">
-        <v>0.29760000000000003</v>
+        <v>0.23064000000000004</v>
       </c>
       <c r="R91">
         <v>35</v>
@@ -15279,7 +15279,7 @@
         <v>4.18</v>
       </c>
       <c r="P92">
-        <v>0.29760000000000003</v>
+        <v>0.23064000000000004</v>
       </c>
       <c r="R92">
         <v>35</v>
@@ -15350,7 +15350,7 @@
         <v>4.18</v>
       </c>
       <c r="P93">
-        <v>0.24645000000000003</v>
+        <v>0.19099875000000002</v>
       </c>
       <c r="R93">
         <v>30</v>
@@ -15421,7 +15421,7 @@
         <v>4.18</v>
       </c>
       <c r="P94">
-        <v>0.24645000000000003</v>
+        <v>0.19099875000000002</v>
       </c>
       <c r="R94">
         <v>30</v>
@@ -15495,7 +15495,7 @@
         <v>4.18</v>
       </c>
       <c r="P95">
-        <v>0.2883</v>
+        <v>0.22343249999999998</v>
       </c>
       <c r="R95">
         <v>30</v>
@@ -15569,7 +15569,7 @@
         <v>4.18</v>
       </c>
       <c r="P96">
-        <v>0.2883</v>
+        <v>0.22343249999999998</v>
       </c>
       <c r="R96">
         <v>30</v>
@@ -15643,7 +15643,7 @@
         <v>4.18</v>
       </c>
       <c r="P97">
-        <v>0.2883</v>
+        <v>0.22343249999999998</v>
       </c>
       <c r="R97">
         <v>30</v>
@@ -15717,7 +15717,7 @@
         <v>4.18</v>
       </c>
       <c r="P98">
-        <v>0.2883</v>
+        <v>0.22343249999999998</v>
       </c>
       <c r="R98">
         <v>30</v>
@@ -15788,7 +15788,7 @@
         <v>4.18</v>
       </c>
       <c r="P99">
-        <v>0.2697</v>
+        <v>0.20901750000000002</v>
       </c>
       <c r="R99">
         <v>30</v>
@@ -15859,7 +15859,7 @@
         <v>4.18</v>
       </c>
       <c r="P100">
-        <v>0.2697</v>
+        <v>0.20901750000000002</v>
       </c>
       <c r="R100">
         <v>30</v>
@@ -15930,7 +15930,7 @@
         <v>4.18</v>
       </c>
       <c r="P101">
-        <v>0.24645000000000003</v>
+        <v>0.19099874999999999</v>
       </c>
       <c r="R101">
         <v>30</v>
@@ -16001,7 +16001,7 @@
         <v>4.18</v>
       </c>
       <c r="P102">
-        <v>0.2697</v>
+        <v>0.20901749999999999</v>
       </c>
       <c r="R102">
         <v>30</v>
@@ -16072,7 +16072,7 @@
         <v>4.18</v>
       </c>
       <c r="P103">
-        <v>0.2697</v>
+        <v>0.20901749999999999</v>
       </c>
       <c r="R103">
         <v>30</v>
@@ -16143,7 +16143,7 @@
         <v>4.18</v>
       </c>
       <c r="P104">
-        <v>0.2697</v>
+        <v>0.20901749999999999</v>
       </c>
       <c r="R104">
         <v>30</v>
@@ -16214,7 +16214,7 @@
         <v>4.18</v>
       </c>
       <c r="P105">
-        <v>0.2697</v>
+        <v>0.20901749999999999</v>
       </c>
       <c r="R105">
         <v>30</v>
@@ -16285,7 +16285,7 @@
         <v>4.18</v>
       </c>
       <c r="P106">
-        <v>0.2697</v>
+        <v>0.20901749999999999</v>
       </c>
       <c r="R106">
         <v>30</v>
@@ -16356,7 +16356,7 @@
         <v>4.18</v>
       </c>
       <c r="P107">
-        <v>0.2697</v>
+        <v>0.20901749999999999</v>
       </c>
       <c r="R107">
         <v>30</v>
@@ -16427,7 +16427,7 @@
         <v>4.5599999999999996</v>
       </c>
       <c r="P108">
-        <v>0.26040000000000002</v>
+        <v>0.20181000000000002</v>
       </c>
       <c r="R108">
         <v>30</v>
@@ -16498,7 +16498,7 @@
         <v>4.5599999999999996</v>
       </c>
       <c r="P109">
-        <v>0.26040000000000002</v>
+        <v>0.20181000000000002</v>
       </c>
       <c r="R109">
         <v>30</v>
@@ -16569,7 +16569,7 @@
         <v>4.18</v>
       </c>
       <c r="P110">
-        <v>0.2883</v>
+        <v>0.22343250000000001</v>
       </c>
       <c r="R110">
         <v>30</v>
@@ -16640,7 +16640,7 @@
         <v>4.18</v>
       </c>
       <c r="P111">
-        <v>0.2883</v>
+        <v>0.22343250000000001</v>
       </c>
       <c r="R111">
         <v>30</v>
@@ -16711,7 +16711,7 @@
         <v>4.18</v>
       </c>
       <c r="P112">
-        <v>0.2883</v>
+        <v>0.22343250000000001</v>
       </c>
       <c r="R112">
         <v>30</v>
@@ -16782,7 +16782,7 @@
         <v>4.18</v>
       </c>
       <c r="P113">
-        <v>0.2883</v>
+        <v>0.22343250000000001</v>
       </c>
       <c r="R113">
         <v>30</v>
@@ -16853,7 +16853,7 @@
         <v>4.18</v>
       </c>
       <c r="P114">
-        <v>0.2883</v>
+        <v>0.22343250000000001</v>
       </c>
       <c r="R114">
         <v>30</v>
@@ -16924,7 +16924,7 @@
         <v>4.18</v>
       </c>
       <c r="P115">
-        <v>0.2697</v>
+        <v>0.20901749999999999</v>
       </c>
       <c r="R115">
         <v>35</v>
@@ -16995,7 +16995,7 @@
         <v>4.18</v>
       </c>
       <c r="P116">
-        <v>0.2697</v>
+        <v>0.20901749999999999</v>
       </c>
       <c r="R116">
         <v>35</v>
@@ -17066,7 +17066,7 @@
         <v>4.18</v>
       </c>
       <c r="P117">
-        <v>0.2697</v>
+        <v>0.20901750000000002</v>
       </c>
       <c r="R117">
         <v>30</v>
@@ -17137,7 +17137,7 @@
         <v>4.18</v>
       </c>
       <c r="P118">
-        <v>0.2697</v>
+        <v>0.20901750000000002</v>
       </c>
       <c r="R118">
         <v>30</v>
@@ -17208,7 +17208,7 @@
         <v>4.18</v>
       </c>
       <c r="P119">
-        <v>0.2697</v>
+        <v>0.20901749999999999</v>
       </c>
       <c r="R119">
         <v>30</v>
@@ -17279,7 +17279,7 @@
         <v>4.18</v>
       </c>
       <c r="P120">
-        <v>0.2697</v>
+        <v>0.20901749999999999</v>
       </c>
       <c r="R120">
         <v>30</v>
@@ -17350,7 +17350,7 @@
         <v>4.18</v>
       </c>
       <c r="P121">
-        <v>0.2697</v>
+        <v>0.20901749999999999</v>
       </c>
       <c r="R121">
         <v>30</v>
@@ -17421,7 +17421,7 @@
         <v>4.18</v>
       </c>
       <c r="P122">
-        <v>0.24645000000000003</v>
+        <v>0.19099874999999999</v>
       </c>
       <c r="R122">
         <v>30</v>
@@ -17492,7 +17492,7 @@
         <v>4.18</v>
       </c>
       <c r="P123">
-        <v>0.24645000000000003</v>
+        <v>0.19099874999999999</v>
       </c>
       <c r="R123">
         <v>30</v>
@@ -17563,7 +17563,7 @@
         <v>4.18</v>
       </c>
       <c r="P124">
-        <v>0.24645000000000003</v>
+        <v>0.19099874999999999</v>
       </c>
       <c r="R124">
         <v>30</v>
@@ -17634,7 +17634,7 @@
         <v>4.18</v>
       </c>
       <c r="P125">
-        <v>0.2697</v>
+        <v>0.20901749999999999</v>
       </c>
       <c r="R125">
         <v>30</v>
@@ -17705,7 +17705,7 @@
         <v>4.18</v>
       </c>
       <c r="P126">
-        <v>0.2697</v>
+        <v>0.20901749999999999</v>
       </c>
       <c r="R126">
         <v>30</v>
@@ -17776,7 +17776,7 @@
         <v>4.7024999999999997</v>
       </c>
       <c r="P127">
-        <v>0.29760000000000003</v>
+        <v>0.23064000000000001</v>
       </c>
       <c r="R127">
         <v>35</v>
@@ -17847,7 +17847,7 @@
         <v>4.7024999999999997</v>
       </c>
       <c r="P128">
-        <v>0.29760000000000003</v>
+        <v>0.23064000000000001</v>
       </c>
       <c r="R128">
         <v>35</v>
@@ -17918,7 +17918,7 @@
         <v>4.7024999999999997</v>
       </c>
       <c r="P129">
-        <v>0.29760000000000003</v>
+        <v>0.23064000000000001</v>
       </c>
       <c r="R129">
         <v>35</v>
@@ -17989,7 +17989,7 @@
         <v>4.7024999999999997</v>
       </c>
       <c r="P130">
-        <v>0.29760000000000003</v>
+        <v>0.23064000000000001</v>
       </c>
       <c r="R130">
         <v>35</v>
@@ -18060,7 +18060,7 @@
         <v>4.7024999999999997</v>
       </c>
       <c r="P131">
-        <v>0.30690000000000001</v>
+        <v>0.23784749999999999</v>
       </c>
       <c r="R131">
         <v>35</v>
@@ -18131,7 +18131,7 @@
         <v>4.7024999999999997</v>
       </c>
       <c r="P132">
-        <v>0.30690000000000001</v>
+        <v>0.23784749999999999</v>
       </c>
       <c r="R132">
         <v>35</v>
@@ -18202,7 +18202,7 @@
         <v>4.7024999999999997</v>
       </c>
       <c r="P133">
-        <v>0.30690000000000001</v>
+        <v>0.23784749999999999</v>
       </c>
       <c r="R133">
         <v>35</v>
@@ -18273,7 +18273,7 @@
         <v>4.7024999999999997</v>
       </c>
       <c r="P134">
-        <v>0.30690000000000001</v>
+        <v>0.23784749999999999</v>
       </c>
       <c r="R134">
         <v>35</v>
@@ -18344,7 +18344,7 @@
         <v>4.7024999999999997</v>
       </c>
       <c r="P135">
-        <v>0.30690000000000001</v>
+        <v>0.23784749999999999</v>
       </c>
       <c r="R135">
         <v>35</v>
@@ -18415,7 +18415,7 @@
         <v>4.7024999999999997</v>
       </c>
       <c r="P136">
-        <v>0.30690000000000001</v>
+        <v>0.23784749999999999</v>
       </c>
       <c r="R136">
         <v>35</v>
@@ -18486,7 +18486,7 @@
         <v>4.7024999999999988</v>
       </c>
       <c r="P137">
-        <v>0.32084999999999997</v>
+        <v>0.24865874999999998</v>
       </c>
       <c r="R137">
         <v>40</v>
@@ -18557,7 +18557,7 @@
         <v>4.2749999999999995</v>
       </c>
       <c r="P138">
-        <v>0.33945000000000003</v>
+        <v>0.26307375000000005</v>
       </c>
       <c r="R138">
         <v>40</v>
@@ -18628,7 +18628,7 @@
         <v>4.7024999999999997</v>
       </c>
       <c r="P139">
-        <v>0.32084999999999997</v>
+        <v>0.24865874999999998</v>
       </c>
       <c r="R139">
         <v>35</v>
@@ -18699,7 +18699,7 @@
         <v>4.2749999999999995</v>
       </c>
       <c r="P140">
-        <v>0.33945000000000003</v>
+        <v>0.26307375000000005</v>
       </c>
       <c r="R140">
         <v>40</v>
@@ -18770,7 +18770,7 @@
         <v>4.2749999999999995</v>
       </c>
       <c r="P141">
-        <v>0.33945000000000003</v>
+        <v>0.26307375000000005</v>
       </c>
       <c r="R141">
         <v>40</v>
@@ -18841,7 +18841,7 @@
         <v>4.2749999999999995</v>
       </c>
       <c r="P142">
-        <v>0.33945000000000003</v>
+        <v>0.26307375000000005</v>
       </c>
       <c r="R142">
         <v>40</v>
@@ -18912,7 +18912,7 @@
         <v>4.2749999999999995</v>
       </c>
       <c r="P143">
-        <v>0.33945000000000003</v>
+        <v>0.26307375000000005</v>
       </c>
       <c r="R143">
         <v>40</v>
@@ -18968,7 +18968,7 @@
         <v>6.9547501182519678E-2</v>
       </c>
       <c r="P144">
-        <v>0.33123000000000002</v>
+        <v>0.25670325000000005</v>
       </c>
     </row>
     <row r="145" spans="1:25" x14ac:dyDescent="0.45">
@@ -19000,7 +19000,7 @@
         <v>3.3660990572339525E-2</v>
       </c>
       <c r="P145">
-        <v>0.33123000000000002</v>
+        <v>0.25670325000000005</v>
       </c>
     </row>
     <row r="146" spans="1:25" x14ac:dyDescent="0.45">
@@ -19032,7 +19032,7 @@
         <v>4.3731468743568369E-2</v>
       </c>
       <c r="P146">
-        <v>0.33123000000000002</v>
+        <v>0.25670325000000005</v>
       </c>
     </row>
     <row r="147" spans="1:25" x14ac:dyDescent="0.45">
@@ -19064,7 +19064,7 @@
         <v>7.8204774129719712E-2</v>
       </c>
       <c r="P147">
-        <v>0.33123000000000002</v>
+        <v>0.25670325000000005</v>
       </c>
     </row>
     <row r="148" spans="1:25" x14ac:dyDescent="0.45">
@@ -19096,7 +19096,7 @@
         <v>0.25801010178695877</v>
       </c>
       <c r="P148">
-        <v>0.33123000000000002</v>
+        <v>0.25670325000000005</v>
       </c>
     </row>
     <row r="149" spans="1:25" x14ac:dyDescent="0.45">
@@ -19128,7 +19128,7 @@
         <v>0.13639655931915756</v>
       </c>
       <c r="P149">
-        <v>0.33123000000000002</v>
+        <v>0.25670325000000005</v>
       </c>
     </row>
     <row r="150" spans="1:25" x14ac:dyDescent="0.45">
@@ -19160,7 +19160,7 @@
         <v>0.15155791457694689</v>
       </c>
       <c r="P150">
-        <v>0.33123000000000002</v>
+        <v>0.25670325000000005</v>
       </c>
     </row>
     <row r="151" spans="1:25" x14ac:dyDescent="0.45">
@@ -19192,7 +19192,7 @@
         <v>2.9488140501388344E-2</v>
       </c>
       <c r="P151">
-        <v>0.33123000000000008</v>
+        <v>0.25670325000000005</v>
       </c>
     </row>
     <row r="152" spans="1:25" x14ac:dyDescent="0.45">
@@ -19224,7 +19224,7 @@
         <v>6.9658777184411699E-2</v>
       </c>
       <c r="P152">
-        <v>0.33123000000000002</v>
+        <v>0.25670325000000005</v>
       </c>
     </row>
     <row r="153" spans="1:25" x14ac:dyDescent="0.45">
@@ -19256,7 +19256,7 @@
         <v>4.7208843802694356E-2</v>
       </c>
       <c r="P153">
-        <v>0.33123000000000002</v>
+        <v>0.25670325000000005</v>
       </c>
     </row>
     <row r="154" spans="1:25" x14ac:dyDescent="0.45">
@@ -19288,7 +19288,7 @@
         <v>8.3178811414293535E-2</v>
       </c>
       <c r="P154">
-        <v>0.33123000000000002</v>
+        <v>0.25670325000000005</v>
       </c>
     </row>
     <row r="155" spans="1:25" x14ac:dyDescent="0.45">
@@ -19320,7 +19320,7 @@
         <v>1.2435093211434519E-2</v>
       </c>
       <c r="P155">
-        <v>0.33123000000000008</v>
+        <v>0.25670325000000005</v>
       </c>
     </row>
     <row r="156" spans="1:25" x14ac:dyDescent="0.45">
@@ -19352,7 +19352,7 @@
         <v>4.7459214806951429E-2</v>
       </c>
       <c r="P156">
-        <v>0.33123000000000002</v>
+        <v>0.25670325000000005</v>
       </c>
     </row>
     <row r="157" spans="1:25" x14ac:dyDescent="0.45">
@@ -19384,7 +19384,7 @@
         <v>0.12900783279352668</v>
       </c>
       <c r="P157">
-        <v>0.33123000000000002</v>
+        <v>0.25670325000000005</v>
       </c>
     </row>
     <row r="158" spans="1:25" x14ac:dyDescent="0.45">

--- a/VerveStacks_ARE_grids_kan/source_data/VerveStacks_ARE.xlsx
+++ b/VerveStacks_ARE_grids_kan/source_data/VerveStacks_ARE.xlsx
@@ -8,16 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\VerveStacks\output\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{ED778446-A099-469D-B7ED-6FAC5DDB21A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{D889CEB1-84B8-4D84-AE9B-B5E67FC5B21D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="weo_pg" sheetId="18" r:id="rId1"/>
-    <sheet name="re_targets" sheetId="17" r:id="rId2"/>
-    <sheet name="ccs_retrofits" sheetId="16" r:id="rId3"/>
-    <sheet name="Calibration" sheetId="15" r:id="rId4"/>
-    <sheet name="existing_stock" sheetId="14" r:id="rId5"/>
+    <sheet name="weo_pg" sheetId="23" r:id="rId1"/>
+    <sheet name="re_targets" sheetId="22" r:id="rId2"/>
+    <sheet name="ccs_retrofits" sheetId="21" r:id="rId3"/>
+    <sheet name="Calibration" sheetId="20" r:id="rId4"/>
+    <sheet name="existing_stock" sheetId="19" r:id="rId5"/>
     <sheet name="historical_data_long" sheetId="5" r:id="rId6"/>
     <sheet name="historical_data" sheetId="4" r:id="rId7"/>
     <sheet name="system_settings" sheetId="1" r:id="rId8"/>
@@ -2249,7 +2249,7 @@
         <xdr:cNvPr id="3" name="Picture 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7D406DD3-49AA-C633-491B-69D891472517}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{76CD5DBD-D5F3-5CA7-1C3F-EA57C7A1CCBE}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2304,7 +2304,7 @@
         <xdr:cNvPr id="3" name="Picture 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{560CFE31-E716-00D2-AE75-90190705A266}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D6D4085C-BE1D-D2AB-4241-742226634FDA}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2655,7 +2655,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BBD81107-6CBF-41F8-B011-978997C6D868}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{043F3502-A733-4EDF-80A5-0B76C69FE9DE}">
   <dimension ref="B2:I111"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -5342,7 +5342,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D814E320-07AB-4279-AE0F-FE3879ADDB24}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C1DF90AC-101B-4819-B7A0-C7D3C721F2A1}">
   <dimension ref="B2:L5"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -5462,7 +5462,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DA638C34-7431-4789-8606-B4CD5E5F787E}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CFF53977-3770-4995-B681-33EB7B5C0E87}">
   <dimension ref="B2:J132"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -9247,7 +9247,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{104B0AB3-4F22-4C25-B22D-DE1F1431BB85}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{35CDE7FF-9743-4EB3-8E7A-0CEE27D5C6A1}">
   <dimension ref="A1:H32"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -9684,7 +9684,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8DDA9136-C63A-4C22-8EBD-519B99CA8837}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3CB96564-26AC-418D-9DB0-3E05F76471AB}">
   <dimension ref="A1:Y197"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
